--- a/List pin Trans_Unlimited2026.xlsx
+++ b/List pin Trans_Unlimited2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/609755e423a5e0ae/Documents/GitHub/MainBoard-Transport-Unlimited2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5404E11-01D1-4602-B4ED-6AFD90F74E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{F5404E11-01D1-4602-B4ED-6AFD90F74E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE600A17-2013-4CC0-B6DB-749AA5910620}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{C03CD885-6ECA-4596-8ECA-71D5F52BB5D3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>komponen</t>
   </si>
@@ -115,6 +115,18 @@
   </si>
   <si>
     <t>ID-BAT</t>
+  </si>
+  <si>
+    <t>RJ45</t>
+  </si>
+  <si>
+    <t>fungsi</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>5V</t>
   </si>
 </sst>
 </file>
@@ -208,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -221,6 +233,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,14 +554,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4BC119F-099C-4C79-A2B3-B7279294D5EC}">
-  <dimension ref="B2:D32"/>
+  <dimension ref="B2:G32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -553,8 +571,14 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
@@ -564,8 +588,14 @@
       <c r="D3" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="1" t="s">
         <v>10</v>
@@ -573,8 +603,14 @@
       <c r="D4" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F4" s="6">
+        <v>2</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
@@ -584,8 +620,14 @@
       <c r="D5" s="1">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -593,8 +635,14 @@
       <c r="D6" s="1">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F6" s="6">
+        <v>4</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
@@ -604,8 +652,14 @@
       <c r="D7" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F7" s="6">
+        <v>5</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="4"/>
       <c r="C8" s="1" t="s">
         <v>10</v>
@@ -613,8 +667,14 @@
       <c r="D8" s="1">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F8" s="6">
+        <v>6</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
@@ -624,8 +684,14 @@
       <c r="D9" s="1">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F9" s="6">
+        <v>7</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="4"/>
       <c r="C10" s="1" t="s">
         <v>10</v>
@@ -633,8 +699,14 @@
       <c r="D10" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="F10" s="6">
+        <v>8</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
@@ -645,7 +717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="4"/>
       <c r="C12" s="1" t="s">
         <v>10</v>
@@ -654,7 +726,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
@@ -665,7 +737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="4"/>
       <c r="C14" s="1" t="s">
         <v>10</v>
@@ -674,7 +746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
@@ -685,7 +757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
